--- a/data/trans_orig/P6710-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2012</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2012 (tasa de respuesta: 98,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19953</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>39476</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64520</t>
+          <t>63903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,42 +899,42 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>9395</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>4185</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>16335</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>7,77%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>9395</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>4449</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>16861</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30448</t>
+          <t>29938</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43861</t>
+          <t>45165</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17468</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50509</t>
+          <t>49130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73183</t>
+          <t>72735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31519</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>51453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88860</t>
+          <t>89099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118480</t>
+          <t>118831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,52%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22450</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35486</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45881</t>
+          <t>46167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>21891</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>42718</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35478</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61544</t>
+          <t>60532</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>23709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35379</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85117</t>
+          <t>84949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112751</t>
+          <t>113013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>53501</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76306</t>
+          <t>76131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148202</t>
+          <t>144649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183517</t>
+          <t>179415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19550</t>
+          <t>20816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>18374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34663</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33438</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48500</t>
+          <t>47145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24733</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>41516</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>65699</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40180</t>
+          <t>41310</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33710</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56104</t>
+          <t>56622</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>37478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60293</t>
+          <t>59200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>25231</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43331</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67190</t>
+          <t>66632</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96557</t>
+          <t>95255</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29972</t>
+          <t>29331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25700</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>21711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41494</t>
+          <t>41664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>24795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48288</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33001</t>
+          <t>33570</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>47278</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73328</t>
+          <t>74341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17650</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37278</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>30289</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35224</t>
+          <t>34466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60622</t>
+          <t>60164</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42987</t>
+          <t>43307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68003</t>
+          <t>68941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26198</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>76488</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106405</t>
+          <t>108660</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16755</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14296</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>32118</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33792</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31963</t>
+          <t>31341</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>38904</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20743</t>
+          <t>20608</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32711</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54741</t>
+          <t>54390</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33273</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25416</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>36269</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34667</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24468</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46403</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>39433</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>61825</t>
+          <t>61798</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>36557</t>
+          <t>36894</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>65605</t>
+          <t>65792</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>93641</t>
+          <t>93338</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19788</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40541</t>
+          <t>40606</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43973</t>
+          <t>43850</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>48164</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>77128</t>
+          <t>77449</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>36066</t>
+          <t>36004</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>54445</t>
+          <t>52991</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>48370</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>78543</t>
+          <t>79349</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>25394</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>48394</t>
+          <t>48191</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>82830</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>117604</t>
+          <t>118863</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>49314</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>77502</t>
+          <t>76453</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>42971</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>77689</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>112182</t>
+          <t>112263</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>74696</t>
+          <t>74373</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>107127</t>
+          <t>107397</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>51907</t>
+          <t>50417</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>78834</t>
+          <t>76645</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>133849</t>
+          <t>133878</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>174819</t>
+          <t>180021</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>27317</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>32952</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>26590</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>52930</t>
+          <t>53699</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>26459</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>33581</t>
+          <t>33320</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>26287</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>52064</t>
+          <t>51739</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>58902</t>
+          <t>59711</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>91594</t>
+          <t>93478</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>41691</t>
+          <t>39759</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>69389</t>
+          <t>67661</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>106633</t>
+          <t>106512</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>148041</t>
+          <t>149660</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>105506</t>
+          <t>106128</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>142016</t>
+          <t>142360</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>69422</t>
+          <t>70320</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>100320</t>
+          <t>102596</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>181300</t>
+          <t>185835</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>232405</t>
+          <t>233831</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>109933</t>
+          <t>110665</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>149300</t>
+          <t>148915</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>61820</t>
+          <t>63294</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>94611</t>
+          <t>94093</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>183274</t>
+          <t>183219</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>233303</t>
+          <t>233834</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>114556</t>
+          <t>114738</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>164220</t>
+          <t>162582</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>100649</t>
+          <t>103443</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>143729</t>
+          <t>145822</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>232853</t>
+          <t>231854</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>298284</t>
+          <t>293419</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>92123</t>
+          <t>90642</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>135760</t>
+          <t>135581</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>72394</t>
+          <t>74131</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>112893</t>
+          <t>112108</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>175147</t>
+          <t>176266</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>231292</t>
+          <t>234070</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>263089</t>
+          <t>265133</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>323334</t>
+          <t>325211</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>153510</t>
+          <t>152244</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>202693</t>
+          <t>203388</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>432261</t>
+          <t>433235</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>511929</t>
+          <t>515575</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>272158</t>
+          <t>269276</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>335218</t>
+          <t>333028</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>164464</t>
+          <t>162389</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>214331</t>
+          <t>211832</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>451391</t>
+          <t>449582</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>533910</t>
+          <t>533129</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>525311</t>
+          <t>529498</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>597471</t>
+          <t>602581</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>333239</t>
+          <t>333069</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>391467</t>
+          <t>393339</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>879634</t>
+          <t>876157</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>977402</t>
+          <t>973936</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2016</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40297</t>
+          <t>39045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63279</t>
+          <t>62280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50339</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75666</t>
+          <t>74762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106992</t>
+          <t>106739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>17737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>17696</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>36517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31165</t>
+          <t>31151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41028</t>
+          <t>41445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>55315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>39938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57154</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88031</t>
+          <t>87483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>33103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>27623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30002</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53980</t>
+          <t>55405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35041</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22150</t>
+          <t>22507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50581</t>
+          <t>51578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38060</t>
+          <t>36918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60476</t>
+          <t>60401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>28826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53303</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83481</t>
+          <t>83118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32087</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22393</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43659</t>
+          <t>43539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68284</t>
+          <t>68913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40188</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62512</t>
+          <t>61454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88994</t>
+          <t>88007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122452</t>
+          <t>121070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>22668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24663</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46046</t>
+          <t>46559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37967</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22699</t>
+          <t>23632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47938</t>
+          <t>47993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33694</t>
+          <t>33853</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52087</t>
+          <t>51071</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76612</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>17078</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35577</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>32376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>55316</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,47 +8936,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>11056</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5935</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>18969</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>7,04%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,57%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11056</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>6288</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>18384</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36758</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>24913</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26785</t>
+          <t>26348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>48180</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34792</t>
+          <t>33481</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>20240</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>31009</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26947</t>
+          <t>27235</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35688</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41022</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62916</t>
+          <t>62741</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27861</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45655</t>
+          <t>45471</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>72497</t>
+          <t>72844</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>102051</t>
+          <t>101571</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27954</t>
+          <t>28872</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39030</t>
+          <t>38262</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59742</t>
+          <t>59763</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>37156</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>32528</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>54706</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>26586</t>
+          <t>25430</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>30080</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>24572</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27968</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>50003</t>
+          <t>49219</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46114</t>
+          <t>46126</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>36925</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>50484</t>
+          <t>51645</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>76565</t>
+          <t>77055</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38672</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>28716</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36883</t>
+          <t>36047</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>59705</t>
+          <t>59985</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18858</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>37781</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>69233</t>
+          <t>70102</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>32107</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>56496</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>79654</t>
+          <t>77788</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>114779</t>
+          <t>115477</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>65270</t>
+          <t>64965</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>97561</t>
+          <t>97188</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>63752</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>95520</t>
+          <t>94009</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>135738</t>
+          <t>135239</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>181281</t>
+          <t>181518</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>76771</t>
+          <t>76537</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>112512</t>
+          <t>112689</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>68098</t>
+          <t>66421</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>97847</t>
+          <t>97760</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>152829</t>
+          <t>153737</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>199869</t>
+          <t>200955</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>42822</t>
+          <t>43696</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>72972</t>
+          <t>73749</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>69962</t>
+          <t>72151</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>105684</t>
+          <t>106659</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>62488</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>95325</t>
+          <t>93528</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>38156</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>65854</t>
+          <t>64085</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>106752</t>
+          <t>106160</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>146936</t>
+          <t>148428</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>21977</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14188</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>51583</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>28357</t>
+          <t>27246</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>51262</t>
+          <t>50562</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>61687</t>
+          <t>60245</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>92705</t>
+          <t>92575</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>82831</t>
+          <t>81968</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>116444</t>
+          <t>115622</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>50682</t>
+          <t>50877</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>78217</t>
+          <t>77433</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>141547</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>182681</t>
+          <t>181803</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>83175</t>
+          <t>83201</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>115594</t>
+          <t>115886</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>68231</t>
+          <t>68854</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>97292</t>
+          <t>97938</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>161390</t>
+          <t>160953</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>203427</t>
+          <t>206638</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>71279</t>
+          <t>70420</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>103129</t>
+          <t>101562</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>31806</t>
+          <t>32548</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>56495</t>
+          <t>56304</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>110485</t>
+          <t>109762</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>149721</t>
+          <t>151260</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>156014</t>
+          <t>156755</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>209125</t>
+          <t>207443</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>135678</t>
+          <t>134522</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>179859</t>
+          <t>182724</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>304203</t>
+          <t>307370</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>372554</t>
+          <t>377543</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>199302</t>
+          <t>197332</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>253631</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>161851</t>
+          <t>166869</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>213099</t>
+          <t>215976</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>375103</t>
+          <t>379011</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>447793</t>
+          <t>454149</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>330543</t>
+          <t>332339</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>396966</t>
+          <t>397845</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>237795</t>
+          <t>236071</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>291371</t>
+          <t>294530</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>587163</t>
+          <t>588022</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>674244</t>
+          <t>675725</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>268041</t>
+          <t>268688</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>330344</t>
+          <t>329628</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>166721</t>
+          <t>166734</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>216769</t>
+          <t>217675</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>451734</t>
+          <t>449150</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>530621</t>
+          <t>530009</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>324521</t>
+          <t>321071</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>390279</t>
+          <t>389656</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>211355</t>
+          <t>208464</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>263673</t>
+          <t>262282</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>548870</t>
+          <t>545625</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>635214</t>
+          <t>635364</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">

--- a/data/trans_orig/P6710-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13892</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>31179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37872</t>
+          <t>39105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63903</t>
+          <t>63958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>30867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45165</t>
+          <t>44512</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24642</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49130</t>
+          <t>50322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72735</t>
+          <t>73373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31880</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51453</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89099</t>
+          <t>89130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118831</t>
+          <t>118509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>35852</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22485</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30477</t>
+          <t>30240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22675</t>
+          <t>23004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46167</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21891</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>35214</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60532</t>
+          <t>60163</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36597</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84949</t>
+          <t>86115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113013</t>
+          <t>113474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>52029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76131</t>
+          <t>74960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144649</t>
+          <t>145752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179415</t>
+          <t>180480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>34707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22567</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>31463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>47806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41516</t>
+          <t>41105</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65699</t>
+          <t>66709</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41310</t>
+          <t>41249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21825</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>34400</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56622</t>
+          <t>57075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37478</t>
+          <t>37453</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59200</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43483</t>
+          <t>43029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66632</t>
+          <t>68001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95255</t>
+          <t>95849</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29331</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25333</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21711</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41664</t>
+          <t>42296</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24795</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>47742</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33570</t>
+          <t>33245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47278</t>
+          <t>46660</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74341</t>
+          <t>74031</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30289</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34466</t>
+          <t>34669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60164</t>
+          <t>59532</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43307</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68941</t>
+          <t>67628</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46650</t>
+          <t>46249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>76488</t>
+          <t>76509</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108660</t>
+          <t>108065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32118</t>
+          <t>32117</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33039</t>
+          <t>34168</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31341</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38904</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20608</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54390</t>
+          <t>54202</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26666</t>
+          <t>26074</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14974</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>34477</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18395</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>36269</t>
+          <t>37733</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>34269</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46241</t>
+          <t>48701</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>39433</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>61798</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>36894</t>
+          <t>36104</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>65792</t>
+          <t>65434</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>93338</t>
+          <t>93282</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40606</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43850</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>46360</t>
+          <t>47257</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>77449</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>34788</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>25733</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28178</t>
+          <t>28720</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>52991</t>
+          <t>53355</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>48923</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>79349</t>
+          <t>80846</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>26496</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>48191</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>81904</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>118863</t>
+          <t>119188</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>49314</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>76453</t>
+          <t>76427</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>42971</t>
+          <t>42248</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>77689</t>
+          <t>78341</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>112263</t>
+          <t>112068</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>74373</t>
+          <t>74048</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>107397</t>
+          <t>107719</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>50417</t>
+          <t>49503</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>76645</t>
+          <t>76307</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>133878</t>
+          <t>132974</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>180021</t>
+          <t>174162</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>26590</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>53699</t>
+          <t>51686</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>32169</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>26287</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>51739</t>
+          <t>53938</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>59322</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>93478</t>
+          <t>92913</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>39759</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>67661</t>
+          <t>68063</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>106512</t>
+          <t>108224</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>149660</t>
+          <t>149679</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>106128</t>
+          <t>104954</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>142360</t>
+          <t>141076</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>70320</t>
+          <t>68978</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>102596</t>
+          <t>100791</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>185835</t>
+          <t>183046</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>233831</t>
+          <t>233971</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>110665</t>
+          <t>111337</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>148915</t>
+          <t>148215</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>62820</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>94093</t>
+          <t>95876</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>183219</t>
+          <t>180108</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>233834</t>
+          <t>231328</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>114738</t>
+          <t>117612</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>162582</t>
+          <t>163242</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>102976</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>145822</t>
+          <t>142747</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>231854</t>
+          <t>230016</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>293419</t>
+          <t>295208</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>90642</t>
+          <t>92345</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>135581</t>
+          <t>134757</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>74131</t>
+          <t>74576</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>112108</t>
+          <t>113999</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>176266</t>
+          <t>175011</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>234070</t>
+          <t>233128</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>265133</t>
+          <t>261695</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>325211</t>
+          <t>323087</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>152244</t>
+          <t>154541</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>203388</t>
+          <t>202533</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>433235</t>
+          <t>429307</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>515575</t>
+          <t>514697</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>269276</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>333028</t>
+          <t>334641</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>162389</t>
+          <t>162682</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>211832</t>
+          <t>216078</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>449582</t>
+          <t>452735</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>533129</t>
+          <t>531013</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>529498</t>
+          <t>525793</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>602581</t>
+          <t>599413</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>333069</t>
+          <t>331589</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>393339</t>
+          <t>392868</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>876157</t>
+          <t>878083</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>973936</t>
+          <t>978907</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39045</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62280</t>
+          <t>62616</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50256</t>
+          <t>51261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74762</t>
+          <t>76733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106739</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28586</t>
+          <t>28392</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36517</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31151</t>
+          <t>32420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41445</t>
+          <t>40905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32931</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55315</t>
+          <t>55194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39938</t>
+          <t>39163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57666</t>
+          <t>58403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87483</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13762</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>32556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27623</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30137</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55405</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>15801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33264</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>23390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27818</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51578</t>
+          <t>51971</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>35965</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60401</t>
+          <t>60848</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>29059</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55186</t>
+          <t>54119</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83118</t>
+          <t>83605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>31964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43539</t>
+          <t>42529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68913</t>
+          <t>67905</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39993</t>
+          <t>39355</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>60315</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88007</t>
+          <t>89561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121070</t>
+          <t>121884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>28447</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>23482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46559</t>
+          <t>46344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>19789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37928</t>
+          <t>39076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>32490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54999</t>
+          <t>55939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>28453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47993</t>
+          <t>47909</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33853</t>
+          <t>33868</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51071</t>
+          <t>50885</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>76081</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>9233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32376</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>55620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17454</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36001</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29078</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48180</t>
+          <t>48833</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27235</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>36211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41897</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62741</t>
+          <t>62587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27313</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>45445</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>72844</t>
+          <t>76016</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>101571</t>
+          <t>101887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>20793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38262</t>
+          <t>37428</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25446</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59763</t>
+          <t>58831</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37156</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>53478</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>27376</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13940</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>30080</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49219</t>
+          <t>49062</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46126</t>
+          <t>46540</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>51645</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77055</t>
+          <t>76807</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38408</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36047</t>
+          <t>35982</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>60983</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>28400</t>
+          <t>28839</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>40481</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>70102</t>
+          <t>68839</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>32254</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>55523</t>
+          <t>56381</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>77788</t>
+          <t>78441</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>115477</t>
+          <t>114428</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>64965</t>
+          <t>65213</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>97188</t>
+          <t>98006</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>63593</t>
+          <t>63486</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>94009</t>
+          <t>92996</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>135239</t>
+          <t>135887</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>181518</t>
+          <t>182150</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>76537</t>
+          <t>76203</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>112689</t>
+          <t>112359</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>66421</t>
+          <t>67375</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>97760</t>
+          <t>98528</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>153737</t>
+          <t>152954</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>200955</t>
+          <t>200619</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>43696</t>
+          <t>43552</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>73749</t>
+          <t>73216</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>43348</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>72151</t>
+          <t>69618</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>106659</t>
+          <t>106820</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>58693</t>
+          <t>61401</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>93528</t>
+          <t>93220</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>38156</t>
+          <t>38634</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>64085</t>
+          <t>65123</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>106160</t>
+          <t>106873</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>148428</t>
+          <t>149849</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>14718</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>50323</t>
+          <t>49779</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27246</t>
+          <t>26462</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>50562</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>60245</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>92575</t>
+          <t>91850</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>81968</t>
+          <t>81424</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>115622</t>
+          <t>115373</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>50877</t>
+          <t>49358</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>77433</t>
+          <t>77690</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>140098</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>181803</t>
+          <t>183217</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>83201</t>
+          <t>83350</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>115886</t>
+          <t>116751</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>68854</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>97938</t>
+          <t>97194</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>160953</t>
+          <t>160065</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>206638</t>
+          <t>203547</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>70420</t>
+          <t>71677</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>101562</t>
+          <t>104487</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>32548</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>56304</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>109762</t>
+          <t>109074</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>151260</t>
+          <t>150522</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>156755</t>
+          <t>155977</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>207443</t>
+          <t>209313</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>134522</t>
+          <t>134300</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>182724</t>
+          <t>180331</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>307370</t>
+          <t>306972</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>377543</t>
+          <t>373003</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>197332</t>
+          <t>195696</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>254758</t>
+          <t>252340</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>166869</t>
+          <t>165494</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>215976</t>
+          <t>212940</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>379011</t>
+          <t>379810</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>454149</t>
+          <t>456150</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>332339</t>
+          <t>331834</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>397845</t>
+          <t>400174</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>236071</t>
+          <t>237273</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>294530</t>
+          <t>292631</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>588022</t>
+          <t>584437</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>675725</t>
+          <t>670724</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>268688</t>
+          <t>267259</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>329628</t>
+          <t>328269</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>166734</t>
+          <t>169858</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>217675</t>
+          <t>217528</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>449150</t>
+          <t>449467</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>530009</t>
+          <t>528774</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>321071</t>
+          <t>323428</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>389656</t>
+          <t>393283</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>208464</t>
+          <t>208440</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>262282</t>
+          <t>263212</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>545625</t>
+          <t>545488</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>635364</t>
+          <t>636334</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
